--- a/KatalonData/ABPTestDataDemo/ABPEditUser_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/ABPEditUser_Demo.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A289401-883E-4C5D-B7BE-BBB41036973E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1763B7-AD49-4385-B90D-F6DE5D183EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
   </bookViews>
   <sheets>
-    <sheet name="OwnerEditPassword" sheetId="17" r:id="rId1"/>
-    <sheet name="CreateDeletePayer" sheetId="13" r:id="rId2"/>
-    <sheet name="CreateDeleteProfileOwner" sheetId="14" r:id="rId3"/>
-    <sheet name="VerifyPasswordPolicy" sheetId="15" r:id="rId4"/>
-    <sheet name="VerifyUsernameLength" sheetId="16" r:id="rId5"/>
+    <sheet name="PayerToOwner" sheetId="20" r:id="rId1"/>
+    <sheet name="PayerEditFields" sheetId="21" r:id="rId2"/>
+    <sheet name="PayerEditPassword" sheetId="22" r:id="rId3"/>
+    <sheet name="OwnerToPayer" sheetId="19" r:id="rId4"/>
+    <sheet name="OwnerEditFields" sheetId="18" r:id="rId5"/>
+    <sheet name="OwnerEditPassword" sheetId="17" r:id="rId6"/>
+    <sheet name="CreateDeletePayer" sheetId="13" r:id="rId7"/>
+    <sheet name="CreateDeleteProfileOwner" sheetId="14" r:id="rId8"/>
+    <sheet name="VerifyPasswordPolicy" sheetId="15" r:id="rId9"/>
+    <sheet name="VerifyUsernameLength" sheetId="16" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="46">
   <si>
     <t>Result</t>
   </si>
@@ -112,16 +117,90 @@
   </si>
   <si>
     <t>t470258@deluxe.com</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>NewEmail</t>
+  </si>
+  <si>
+    <t>t11111@deluxe.com</t>
+  </si>
+  <si>
+    <t>t22222@deluxe.com</t>
+  </si>
+  <si>
+    <t>create Owner+ change it's password (non logged in user)</t>
+  </si>
+  <si>
+    <t>t33333@deluxe.com</t>
+  </si>
+  <si>
+    <t>create Owner+ change it's value+ verify User Name, Name, Role, edit, delete links (non logged in user)</t>
+  </si>
+  <si>
+    <t>2026-08-10 19:01:59</t>
+  </si>
+  <si>
+    <t>t55555@deluxe.com</t>
+  </si>
+  <si>
+    <t>t66666@deluxe.com</t>
+  </si>
+  <si>
+    <t>create Owner+ change Owner to Payer+ verify User Name, Role (non logged in user)</t>
+  </si>
+  <si>
+    <t>create Payer+ change it's value+ verify User Name, Name, Role, edit, delete links (non logged in user)</t>
+  </si>
+  <si>
+    <t>create Payer+ change Payer to Owner+ verify User Name, Role (non logged in user)</t>
+  </si>
+  <si>
+    <t>2026-08-11 19:10:42</t>
+  </si>
+  <si>
+    <t>Tue Aug 11 22:12:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 11 22:15:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 12 16:46:35 IST 2026</t>
+  </si>
+  <si>
+    <t>create Payer+ change it's password (non logged in user)</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Wed Aug 12 19:05:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 12 19:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 12 19:08:56 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
@@ -169,10 +248,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -196,8 +276,21 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -529,19 +622,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FBC738-058D-40B6-8A98-4CBF68B78125}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79063EF-61F9-4893-B046-702D0888B9B3}">
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" style="5"/>
-    <col min="3" max="3" width="20.7265625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="5"/>
-    <col min="5" max="5" width="15" style="5" customWidth="1"/>
-    <col min="6" max="6" width="19.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" style="5" width="8.7265625"/>
+    <col min="2" max="2" customWidth="true" style="5" width="13.26953125"/>
+    <col min="3" max="3" customWidth="true" style="5" width="54.36328125"/>
+    <col min="4" max="4" style="5" width="8.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="5" width="19.81640625"/>
+    <col min="6" max="6" customWidth="true" style="5" width="17.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="5" width="18.81640625"/>
+    <col min="8" max="16384" style="5" width="8.7265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -555,33 +650,488 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>23</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1177889900</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{CAA852A0-E0D1-40F8-84E8-883CBBD2C927}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{FE79C1AB-0827-47B4-A1B0-1C74EE80B85E}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{5C5221EB-B97F-415C-84DA-D0C5E15135EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6449346E-627A-4484-9036-DF9C330EC51E}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="42.08984375"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C7002F-0144-4C31-979C-CE4105F6610D}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="5" width="8.7265625"/>
+    <col min="2" max="2" customWidth="true" style="5" width="14.90625"/>
+    <col min="3" max="3" customWidth="true" style="7" width="57.36328125"/>
+    <col min="4" max="4" style="5" width="8.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="5" width="19.81640625"/>
+    <col min="6" max="6" customWidth="true" style="5" width="19.81640625"/>
+    <col min="7" max="7" customWidth="true" style="5" width="22.54296875"/>
+    <col min="8" max="16384" style="5" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9">
+        <v>2233445566</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1177889900</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{5E738090-C66F-4055-AFF1-D6F262BEDD18}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{303784BE-5561-4B96-9F8D-565862C296BB}"/>
+    <hyperlink ref="E3" r:id="rId3" xr:uid="{26A297A8-0A3B-444E-90C4-5B121C5A45FE}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{C668DAE5-9274-4EC1-9ADA-DCB73BFC10D8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F6E7DE-94D6-4475-8EE0-0EB6E32C0E61}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="5" width="8.7265625"/>
+    <col min="2" max="2" customWidth="true" style="5" width="13.26953125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="5" width="52.7265625"/>
+    <col min="4" max="4" style="5" width="8.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="5" width="19.81640625"/>
+    <col min="6" max="6" customWidth="true" style="5" width="17.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="5" width="18.81640625"/>
+    <col min="8" max="16384" style="5" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9">
+        <v>9876543210</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{46465BDC-B259-4BBF-A196-9BB17840986B}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{BEE6D388-A596-45C7-853D-B327C8A89FFF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD9E5DF-CE2C-499A-ABD7-3C7B1AC58117}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="5" width="8.7265625"/>
+    <col min="2" max="2" customWidth="true" style="5" width="13.26953125"/>
+    <col min="3" max="3" customWidth="true" style="5" width="54.36328125"/>
+    <col min="4" max="4" style="5" width="8.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="5" width="19.81640625"/>
+    <col min="6" max="6" customWidth="true" style="5" width="17.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="5" width="18.81640625"/>
+    <col min="8" max="16384" style="5" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9">
+        <v>9876543210</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{2F26CA2C-4CEC-49D2-AEC8-23DD0AC938AE}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{29AD6F35-3779-4595-A1F2-B54883FF4920}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413613D0-4F35-41BD-B8FD-E5B2FE75DD52}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" style="5" width="8.7265625"/>
+    <col min="3" max="3" customWidth="true" style="7" width="57.36328125"/>
+    <col min="4" max="4" style="5" width="8.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="5" width="19.81640625"/>
+    <col min="6" max="6" customWidth="true" style="5" width="19.81640625"/>
+    <col min="7" max="7" customWidth="true" style="5" width="22.54296875"/>
+    <col min="8" max="16384" style="5" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9">
+        <v>9876543210</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1234567890</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{CD2D85EE-0CD5-43F2-9BEB-CDB75659E8DE}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{40E34726-323D-4D61-A1E0-C9533EA045D3}"/>
+    <hyperlink ref="E3" r:id="rId3" xr:uid="{794D4750-FEDC-4A73-9605-E1CAF7B74EE6}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{DBDBC3C8-03A9-4376-A6A3-5AD450498A6C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FBC738-058D-40B6-8A98-4CBF68B78125}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="5" width="8.7265625"/>
+    <col min="2" max="2" customWidth="true" style="5" width="13.26953125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="5" width="52.7265625"/>
+    <col min="4" max="4" style="5" width="8.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="5" width="19.81640625"/>
+    <col min="6" max="6" customWidth="true" style="5" width="17.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="5" width="18.81640625"/>
+    <col min="8" max="16384" style="5" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9">
+        <v>9876543210</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{CAA852A0-E0D1-40F8-84E8-883CBBD2C927}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{7CB93EF6-E71F-4ECA-8681-0502D332DCA8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF22AAA-B408-4BD0-AFCC-6311E82FCB07}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -604,10 +1154,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>18</v>
       </c>
       <c r="C2" s="3"/>
@@ -623,7 +1173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16985F12-B56F-4D06-B670-F5B0F040BD4C}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -646,10 +1196,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>19</v>
       </c>
       <c r="C2" s="3"/>
@@ -665,18 +1215,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07D28A9-3334-4E80-A64C-A7B4C1579E51}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="5"/>
-    <col min="2" max="2" width="25.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.7265625" style="5"/>
-    <col min="5" max="5" width="11.90625" style="5" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="19.81640625" style="5" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="79.6328125" style="5" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" style="5" width="8.7265625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="5" width="25.36328125"/>
+    <col min="3" max="4" style="5" width="8.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="5" width="11.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="5" width="19.81640625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="5" width="79.6328125" collapsed="true"/>
+    <col min="8" max="16384" style="5" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -760,61 +1310,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6449346E-627A-4484-9036-DF9C330EC51E}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="6" max="6" width="42.08984375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>